--- a/data/trans_orig/P33B_R1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R1-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>28422</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42182</t>
+          <t>38479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41650</t>
+          <t>45232</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33862</t>
+          <t>37201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50253</t>
+          <t>54608</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70708</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58042</t>
+          <t>61668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86408</t>
+          <t>88855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>282385</t>
+          <t>290423</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269261</t>
+          <t>280366</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291590</t>
+          <t>299364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>247985</t>
+          <t>270829</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239382</t>
+          <t>261453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255773</t>
+          <t>278860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>530369</t>
+          <t>561252</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514669</t>
+          <t>546051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>543035</t>
+          <t>573238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>40442</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28374</t>
+          <t>27154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60423</t>
+          <t>57795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57573</t>
+          <t>58834</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46749</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69694</t>
+          <t>70866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>98327</t>
+          <t>99276</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81459</t>
+          <t>81579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121647</t>
+          <t>122881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>477636</t>
+          <t>490205</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>457967</t>
+          <t>472852</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490016</t>
+          <t>503493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>457396</t>
+          <t>487660</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445275</t>
+          <t>475628</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>468220</t>
+          <t>500201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>935032</t>
+          <t>977865</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911712</t>
+          <t>954260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>951900</t>
+          <t>995562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43203</t>
+          <t>43915</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32310</t>
+          <t>33117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54793</t>
+          <t>56147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>76051</t>
+          <t>77381</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63116</t>
+          <t>64561</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88025</t>
+          <t>90522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>119254</t>
+          <t>121296</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102497</t>
+          <t>104423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135485</t>
+          <t>139254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>272847</t>
+          <t>272078</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>261257</t>
+          <t>259846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283740</t>
+          <t>282876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>272008</t>
+          <t>277893</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260034</t>
+          <t>264752</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>284943</t>
+          <t>290713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>544855</t>
+          <t>549971</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>528624</t>
+          <t>532013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>561612</t>
+          <t>566844</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348059</t>
+          <t>355274</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348059</t>
+          <t>355274</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348059</t>
+          <t>355274</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664109</t>
+          <t>671267</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664109</t>
+          <t>671267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664109</t>
+          <t>671267</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44821</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>35481</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60994</t>
+          <t>66913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85768</t>
+          <t>95081</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54137</t>
+          <t>81081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111873</t>
+          <t>113321</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>130589</t>
+          <t>144727</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93989</t>
+          <t>122710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>156168</t>
+          <t>167055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>267736</t>
+          <t>323499</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251563</t>
+          <t>306232</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280375</t>
+          <t>337664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>389950</t>
+          <t>326880</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363845</t>
+          <t>308640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>421581</t>
+          <t>340880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>657685</t>
+          <t>650380</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>632106</t>
+          <t>628052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694285</t>
+          <t>672397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>21903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28873</t>
+          <t>31223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36532</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29572</t>
+          <t>32098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45460</t>
+          <t>48282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>165077</t>
+          <t>191120</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158748</t>
+          <t>183762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169780</t>
+          <t>196134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>185406</t>
+          <t>201792</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179401</t>
+          <t>195600</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190573</t>
+          <t>207330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>350484</t>
+          <t>392912</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341556</t>
+          <t>384206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357444</t>
+          <t>400390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30093</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>21791</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40434</t>
+          <t>40320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>62891</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51225</t>
+          <t>53024</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71411</t>
+          <t>74242</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>90445</t>
+          <t>92975</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77448</t>
+          <t>79901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103940</t>
+          <t>105924</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239543</t>
+          <t>240623</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229202</t>
+          <t>230387</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247226</t>
+          <t>248916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>196704</t>
+          <t>200859</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185645</t>
+          <t>189508</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205831</t>
+          <t>210726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>436247</t>
+          <t>441482</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>422752</t>
+          <t>428533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>449244</t>
+          <t>454556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>76439</t>
+          <t>87726</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59522</t>
+          <t>70445</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99172</t>
+          <t>110589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>139097</t>
+          <t>173594</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65066</t>
+          <t>151330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>191055</t>
+          <t>195279</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>215537</t>
+          <t>261320</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>141497</t>
+          <t>232826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>261449</t>
+          <t>294654</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>546811</t>
+          <t>630879</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>524078</t>
+          <t>608016</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>563728</t>
+          <t>648160</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>710168</t>
+          <t>598463</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>658210</t>
+          <t>576778</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>784199</t>
+          <t>620727</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1256977</t>
+          <t>1229342</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1211065</t>
+          <t>1196008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1331017</t>
+          <t>1257836</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>138211</t>
+          <t>154567</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65374</t>
+          <t>134810</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>197729</t>
+          <t>176044</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>222701</t>
+          <t>255948</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>202936</t>
+          <t>231288</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>243335</t>
+          <t>277861</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>360912</t>
+          <t>410515</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>225109</t>
+          <t>378957</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>434513</t>
+          <t>443796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>790509</t>
+          <t>643505</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>730991</t>
+          <t>622028</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>863346</t>
+          <t>663262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>492691</t>
+          <t>574661</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>472057</t>
+          <t>552748</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>512456</t>
+          <t>599321</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1283200</t>
+          <t>1218166</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1209599</t>
+          <t>1184885</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1419003</t>
+          <t>1249724</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>76,73%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>416243</t>
+          <t>449347</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>331078</t>
+          <t>410856</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>468750</t>
+          <t>488805</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>706060</t>
+          <t>793993</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>561591</t>
+          <t>752721</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>771546</t>
+          <t>835932</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1122303</t>
+          <t>1243340</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>975390</t>
+          <t>1183311</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1214311</t>
+          <t>1308982</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3042544</t>
+          <t>3082333</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2990037</t>
+          <t>3042875</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3127709</t>
+          <t>3120824</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2952306</t>
+          <t>2939037</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2886820</t>
+          <t>2897098</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3096775</t>
+          <t>2980309</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5994851</t>
+          <t>6021370</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5902843</t>
+          <t>5955728</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6141764</t>
+          <t>6081399</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
